--- a/artfynd/A 23729-2024 artfynd.xlsx
+++ b/artfynd/A 23729-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>69300081</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528782.0274146862</v>
+        <v>528782</v>
       </c>
       <c r="R2" t="n">
-        <v>6987391.865337197</v>
+        <v>6987392</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69300083</v>
+        <v>112550273</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,34 +806,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528927.1427326025</v>
+        <v>528990</v>
       </c>
       <c r="R3" t="n">
-        <v>6987285.96400347</v>
+        <v>6987098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,76 +880,60 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69300084</v>
+        <v>69300082</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -985,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528926.9406997486</v>
+        <v>528927</v>
       </c>
       <c r="R4" t="n">
-        <v>6987155.1520377</v>
+        <v>6987286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,21 +976,11 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1049,12 +997,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1062,7 +1010,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Sälg # Salix caprea</t>
+          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,37 +1028,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69300085</v>
+        <v>69300083</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1120,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528926.9406997486</v>
+        <v>528927</v>
       </c>
       <c r="R5" t="n">
-        <v>6987155.1520377</v>
+        <v>6987286</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,21 +1096,11 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1184,12 +1117,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1197,7 +1130,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # Sälg # Salix caprea</t>
+          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1215,37 +1148,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69300082</v>
+        <v>69300085</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1255,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528927.1427326025</v>
+        <v>528927</v>
       </c>
       <c r="R6" t="n">
-        <v>6987285.96400347</v>
+        <v>6987155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,21 +1216,11 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1319,12 +1237,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1332,7 +1250,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
+          <t>1 substratenheter # Sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1347,6 +1265,352 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>69300084</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528927</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6987155</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Sälg # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112550270</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529015</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6987126</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112550271</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>528948</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6987071</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23729-2024 artfynd.xlsx
+++ b/artfynd/A 23729-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300082</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300083</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300085</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1385,6 +1415,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300084</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1498,6 +1533,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550270</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1611,8 +1651,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>